--- a/backtest_runs/20260410_193731/by_symbol/FPRM/FPRM.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/FPRM/FPRM.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
         <v>-1693.650000000007</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>100241.95</v>
@@ -633,7 +633,7 @@
         <v>-9516.699999999997</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>90725.25</v>
@@ -863,7 +863,7 @@
         <v>-564.5500000000023</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>105161.6</v>
@@ -955,7 +955,7 @@
         <v>-7984.350000000001</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>97177.25</v>
@@ -1139,7 +1139,7 @@
         <v>-6532.650000000004</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>97983.75</v>
@@ -1185,7 +1185,7 @@
         <v>-80.64999999999829</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>97903.10000000001</v>
